--- a/UTCUTS/A1_Outputs/reference_freeze/A-O_Parametrization.xlsx
+++ b/UTCUTS/A1_Outputs/reference_freeze/A-O_Parametrization.xlsx
@@ -63901,7 +63901,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3DCDC40-DE74-4D49-8E7C-66A5B9A9ABAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C358542C-09FB-4679-85FC-00FAC1BA0F41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
